--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4051" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4051" uniqueCount="320">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:37:51+00:00</t>
+    <t>2023-09-19T16:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -134,6 +134,10 @@
   </si>
   <si>
     <t>A container for a collection of resources.</t>
+  </si>
+  <si>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -1448,16 +1452,16 @@
         <v>34</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AN1" t="s" s="2">
         <v>34</v>
@@ -1465,10 +1469,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1479,7 +1483,7 @@
         <v>35</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>34</v>
@@ -1488,19 +1492,19 @@
         <v>34</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1550,13 +1554,13 @@
         <v>34</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>34</v>
@@ -1579,10 +1583,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1593,7 +1597,7 @@
         <v>35</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>34</v>
@@ -1602,16 +1606,16 @@
         <v>34</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1662,25 +1666,25 @@
         <v>34</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM3" t="s" s="2">
         <v>34</v>
@@ -1691,10 +1695,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1705,28 +1709,28 @@
         <v>35</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1776,25 +1780,25 @@
         <v>34</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>34</v>
@@ -1805,10 +1809,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1819,7 +1823,7 @@
         <v>35</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>34</v>
@@ -1831,16 +1835,16 @@
         <v>34</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1866,13 +1870,13 @@
         <v>34</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>34</v>
@@ -1890,25 +1894,25 @@
         <v>34</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>34</v>
@@ -1919,10 +1923,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1933,7 +1937,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>34</v>
@@ -1942,19 +1946,19 @@
         <v>34</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2004,39 +2008,39 @@
         <v>34</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2044,10 +2048,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>34</v>
@@ -2056,19 +2060,19 @@
         <v>34</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2079,7 +2083,7 @@
         <v>34</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T7" t="s" s="2">
         <v>34</v>
@@ -2094,13 +2098,13 @@
         <v>34</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>34</v>
@@ -2118,39 +2122,39 @@
         <v>34</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2161,7 +2165,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>34</v>
@@ -2170,19 +2174,19 @@
         <v>34</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2232,39 +2236,39 @@
         <v>34</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2275,7 +2279,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>34</v>
@@ -2284,19 +2288,19 @@
         <v>34</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2346,25 +2350,25 @@
         <v>34</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>34</v>
@@ -2375,10 +2379,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2398,19 +2402,19 @@
         <v>34</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2460,7 +2464,7 @@
         <v>34</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>35</v>
@@ -2469,16 +2473,16 @@
         <v>36</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>34</v>
@@ -2489,10 +2493,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2503,7 +2507,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>34</v>
@@ -2515,13 +2519,13 @@
         <v>34</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2572,13 +2576,13 @@
         <v>34</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>34</v>
@@ -2590,7 +2594,7 @@
         <v>34</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>34</v>
@@ -2601,14 +2605,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2627,16 +2631,16 @@
         <v>34</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2674,19 +2678,19 @@
         <v>34</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>35</v>
@@ -2695,16 +2699,16 @@
         <v>36</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>34</v>
@@ -2715,14 +2719,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2735,25 +2739,25 @@
         <v>34</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>34</v>
@@ -2802,7 +2806,7 @@
         <v>34</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>35</v>
@@ -2811,16 +2815,16 @@
         <v>36</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>34</v>
@@ -2831,10 +2835,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2842,10 +2846,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>34</v>
@@ -2854,19 +2858,19 @@
         <v>34</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2916,25 +2920,25 @@
         <v>34</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>34</v>
@@ -2945,10 +2949,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2956,10 +2960,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>34</v>
@@ -2968,19 +2972,19 @@
         <v>34</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3030,25 +3034,25 @@
         <v>34</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>34</v>
@@ -3059,10 +3063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3070,7 +3074,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>36</v>
@@ -3082,16 +3086,16 @@
         <v>34</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3130,19 +3134,19 @@
         <v>34</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>35</v>
@@ -3151,16 +3155,16 @@
         <v>36</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>34</v>
@@ -3171,10 +3175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3185,7 +3189,7 @@
         <v>35</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>34</v>
@@ -3197,13 +3201,13 @@
         <v>34</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3254,13 +3258,13 @@
         <v>34</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>34</v>
@@ -3272,7 +3276,7 @@
         <v>34</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>34</v>
@@ -3283,14 +3287,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3309,16 +3313,16 @@
         <v>34</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3356,19 +3360,19 @@
         <v>34</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>35</v>
@@ -3377,16 +3381,16 @@
         <v>36</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>34</v>
@@ -3397,14 +3401,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3417,25 +3421,25 @@
         <v>34</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>34</v>
@@ -3484,7 +3488,7 @@
         <v>34</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>35</v>
@@ -3493,16 +3497,16 @@
         <v>36</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>34</v>
@@ -3513,10 +3517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3536,16 +3540,16 @@
         <v>34</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>37</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3596,7 +3600,7 @@
         <v>34</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>35</v>
@@ -3625,10 +3629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3639,7 +3643,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>34</v>
@@ -3648,19 +3652,19 @@
         <v>34</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3710,25 +3714,25 @@
         <v>34</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>34</v>
@@ -3739,10 +3743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3753,7 +3757,7 @@
         <v>35</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>34</v>
@@ -3762,16 +3766,16 @@
         <v>34</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3822,13 +3826,13 @@
         <v>34</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>34</v>
@@ -3840,7 +3844,7 @@
         <v>34</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>34</v>
@@ -3851,10 +3855,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3865,7 +3869,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>34</v>
@@ -3874,16 +3878,16 @@
         <v>34</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3934,25 +3938,25 @@
         <v>34</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>34</v>
@@ -3963,10 +3967,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3977,7 +3981,7 @@
         <v>35</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>34</v>
@@ -3989,13 +3993,13 @@
         <v>34</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4046,13 +4050,13 @@
         <v>34</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>34</v>
@@ -4064,7 +4068,7 @@
         <v>34</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>34</v>
@@ -4075,14 +4079,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4101,16 +4105,16 @@
         <v>34</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4148,19 +4152,19 @@
         <v>34</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>35</v>
@@ -4169,16 +4173,16 @@
         <v>36</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>34</v>
@@ -4189,14 +4193,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4209,25 +4213,25 @@
         <v>34</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>34</v>
@@ -4276,7 +4280,7 @@
         <v>34</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>35</v>
@@ -4285,16 +4289,16 @@
         <v>36</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>34</v>
@@ -4305,10 +4309,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4319,7 +4323,7 @@
         <v>35</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>34</v>
@@ -4328,19 +4332,19 @@
         <v>34</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4366,13 +4370,13 @@
         <v>34</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>34</v>
@@ -4390,25 +4394,25 @@
         <v>34</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>34</v>
@@ -4419,10 +4423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4433,7 +4437,7 @@
         <v>35</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>34</v>
@@ -4442,19 +4446,19 @@
         <v>34</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4504,25 +4508,25 @@
         <v>34</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>34</v>
@@ -4533,10 +4537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4547,7 +4551,7 @@
         <v>35</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>34</v>
@@ -4556,16 +4560,16 @@
         <v>34</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4616,25 +4620,25 @@
         <v>34</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>34</v>
@@ -4645,10 +4649,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4659,7 +4663,7 @@
         <v>35</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>34</v>
@@ -4671,13 +4675,13 @@
         <v>34</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4728,13 +4732,13 @@
         <v>34</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>34</v>
@@ -4746,7 +4750,7 @@
         <v>34</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>34</v>
@@ -4757,14 +4761,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4783,16 +4787,16 @@
         <v>34</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4830,19 +4834,19 @@
         <v>34</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>35</v>
@@ -4851,16 +4855,16 @@
         <v>36</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>34</v>
@@ -4871,14 +4875,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4891,25 +4895,25 @@
         <v>34</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>34</v>
@@ -4958,7 +4962,7 @@
         <v>34</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>35</v>
@@ -4967,16 +4971,16 @@
         <v>36</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>34</v>
@@ -4987,10 +4991,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4998,10 +5002,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>34</v>
@@ -5010,19 +5014,19 @@
         <v>34</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5048,13 +5052,13 @@
         <v>34</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>34</v>
@@ -5072,25 +5076,25 @@
         <v>34</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>34</v>
@@ -5101,10 +5105,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5112,10 +5116,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>34</v>
@@ -5124,19 +5128,19 @@
         <v>34</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5186,25 +5190,25 @@
         <v>34</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>34</v>
@@ -5215,10 +5219,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5229,7 +5233,7 @@
         <v>35</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>34</v>
@@ -5238,19 +5242,19 @@
         <v>34</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5300,25 +5304,25 @@
         <v>34</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>34</v>
@@ -5329,10 +5333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5343,7 +5347,7 @@
         <v>35</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>34</v>
@@ -5352,19 +5356,19 @@
         <v>34</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5414,25 +5418,25 @@
         <v>34</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>34</v>
@@ -5443,10 +5447,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5457,7 +5461,7 @@
         <v>35</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>34</v>
@@ -5466,19 +5470,19 @@
         <v>34</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5528,25 +5532,25 @@
         <v>34</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>34</v>
@@ -5557,10 +5561,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5571,7 +5575,7 @@
         <v>35</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>34</v>
@@ -5580,19 +5584,19 @@
         <v>34</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5642,25 +5646,25 @@
         <v>34</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>34</v>
@@ -5671,10 +5675,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5685,7 +5689,7 @@
         <v>35</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>34</v>
@@ -5694,16 +5698,16 @@
         <v>34</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5754,25 +5758,25 @@
         <v>34</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>34</v>
@@ -5783,10 +5787,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5797,7 +5801,7 @@
         <v>35</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>34</v>
@@ -5809,13 +5813,13 @@
         <v>34</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5866,13 +5870,13 @@
         <v>34</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>34</v>
@@ -5884,7 +5888,7 @@
         <v>34</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>34</v>
@@ -5895,14 +5899,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5921,16 +5925,16 @@
         <v>34</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5968,19 +5972,19 @@
         <v>34</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>35</v>
@@ -5989,16 +5993,16 @@
         <v>36</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>34</v>
@@ -6009,14 +6013,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6029,25 +6033,25 @@
         <v>34</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>34</v>
@@ -6096,7 +6100,7 @@
         <v>34</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>35</v>
@@ -6105,16 +6109,16 @@
         <v>36</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>34</v>
@@ -6125,10 +6129,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6136,10 +6140,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>34</v>
@@ -6148,19 +6152,19 @@
         <v>34</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6210,25 +6214,25 @@
         <v>34</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>34</v>
@@ -6239,10 +6243,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6253,7 +6257,7 @@
         <v>35</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>34</v>
@@ -6262,19 +6266,19 @@
         <v>34</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6324,25 +6328,25 @@
         <v>34</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>34</v>
@@ -6353,10 +6357,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6367,7 +6371,7 @@
         <v>35</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>34</v>
@@ -6376,19 +6380,19 @@
         <v>34</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6438,25 +6442,25 @@
         <v>34</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>34</v>
@@ -6467,10 +6471,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6481,7 +6485,7 @@
         <v>35</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>34</v>
@@ -6490,19 +6494,19 @@
         <v>34</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6552,25 +6556,25 @@
         <v>34</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>34</v>
@@ -6581,10 +6585,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6595,7 +6599,7 @@
         <v>35</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>34</v>
@@ -6604,19 +6608,19 @@
         <v>34</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6666,13 +6670,13 @@
         <v>34</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>34</v>
@@ -6684,7 +6688,7 @@
         <v>34</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>34</v>
@@ -6695,23 +6699,23 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>34</v>
@@ -6720,16 +6724,16 @@
         <v>34</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6780,7 +6784,7 @@
         <v>34</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>35</v>
@@ -6789,16 +6793,16 @@
         <v>36</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>34</v>
@@ -6809,10 +6813,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6823,7 +6827,7 @@
         <v>35</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>34</v>
@@ -6835,13 +6839,13 @@
         <v>34</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6892,13 +6896,13 @@
         <v>34</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>34</v>
@@ -6910,7 +6914,7 @@
         <v>34</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>34</v>
@@ -6921,14 +6925,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6947,16 +6951,16 @@
         <v>34</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6994,19 +6998,19 @@
         <v>34</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>35</v>
@@ -7015,16 +7019,16 @@
         <v>36</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>34</v>
@@ -7035,14 +7039,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7055,25 +7059,25 @@
         <v>34</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>34</v>
@@ -7122,7 +7126,7 @@
         <v>34</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>35</v>
@@ -7131,16 +7135,16 @@
         <v>36</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>34</v>
@@ -7151,10 +7155,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7174,16 +7178,16 @@
         <v>34</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>37</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7234,7 +7238,7 @@
         <v>34</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>35</v>
@@ -7263,10 +7267,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7277,7 +7281,7 @@
         <v>35</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>34</v>
@@ -7286,19 +7290,19 @@
         <v>34</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7348,25 +7352,25 @@
         <v>34</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>34</v>
@@ -7377,21 +7381,21 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>34</v>
@@ -7403,16 +7407,16 @@
         <v>34</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7462,25 +7466,25 @@
         <v>34</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>34</v>
@@ -7491,10 +7495,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7505,7 +7509,7 @@
         <v>35</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>34</v>
@@ -7514,16 +7518,16 @@
         <v>34</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7574,25 +7578,25 @@
         <v>34</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>34</v>
@@ -7603,10 +7607,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7617,7 +7621,7 @@
         <v>35</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>34</v>
@@ -7629,13 +7633,13 @@
         <v>34</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7686,13 +7690,13 @@
         <v>34</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>34</v>
@@ -7704,7 +7708,7 @@
         <v>34</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>34</v>
@@ -7715,14 +7719,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7741,16 +7745,16 @@
         <v>34</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7788,19 +7792,19 @@
         <v>34</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>35</v>
@@ -7809,16 +7813,16 @@
         <v>36</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>34</v>
@@ -7829,14 +7833,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7849,25 +7853,25 @@
         <v>34</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>34</v>
@@ -7916,7 +7920,7 @@
         <v>34</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>35</v>
@@ -7925,16 +7929,16 @@
         <v>36</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>34</v>
@@ -7945,10 +7949,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7959,7 +7963,7 @@
         <v>35</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>34</v>
@@ -7968,19 +7972,19 @@
         <v>34</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8006,13 +8010,13 @@
         <v>34</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>34</v>
@@ -8030,25 +8034,25 @@
         <v>34</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>34</v>
@@ -8059,10 +8063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8073,7 +8077,7 @@
         <v>35</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>34</v>
@@ -8082,19 +8086,19 @@
         <v>34</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8144,25 +8148,25 @@
         <v>34</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>34</v>
@@ -8173,10 +8177,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8184,10 +8188,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>34</v>
@@ -8196,16 +8200,16 @@
         <v>34</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8256,25 +8260,25 @@
         <v>34</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>34</v>
@@ -8285,10 +8289,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8299,7 +8303,7 @@
         <v>35</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>34</v>
@@ -8311,13 +8315,13 @@
         <v>34</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8368,13 +8372,13 @@
         <v>34</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>34</v>
@@ -8386,7 +8390,7 @@
         <v>34</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>34</v>
@@ -8397,14 +8401,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8423,16 +8427,16 @@
         <v>34</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8470,19 +8474,19 @@
         <v>34</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>35</v>
@@ -8491,16 +8495,16 @@
         <v>36</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>34</v>
@@ -8511,14 +8515,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8531,25 +8535,25 @@
         <v>34</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>34</v>
@@ -8598,7 +8602,7 @@
         <v>34</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>35</v>
@@ -8607,16 +8611,16 @@
         <v>36</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>34</v>
@@ -8627,10 +8631,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8638,10 +8642,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>34</v>
@@ -8650,19 +8654,19 @@
         <v>34</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8673,7 +8677,7 @@
         <v>34</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>34</v>
@@ -8688,13 +8692,13 @@
         <v>34</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>34</v>
@@ -8712,25 +8716,25 @@
         <v>34</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>34</v>
@@ -8741,10 +8745,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8752,10 +8756,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>34</v>
@@ -8764,19 +8768,19 @@
         <v>34</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8787,7 +8791,7 @@
         <v>34</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>34</v>
@@ -8826,25 +8830,25 @@
         <v>34</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>34</v>
@@ -8855,10 +8859,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8869,7 +8873,7 @@
         <v>35</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>34</v>
@@ -8878,19 +8882,19 @@
         <v>34</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8940,25 +8944,25 @@
         <v>34</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>34</v>
@@ -8969,10 +8973,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8983,7 +8987,7 @@
         <v>35</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>34</v>
@@ -8992,19 +8996,19 @@
         <v>34</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9054,25 +9058,25 @@
         <v>34</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>34</v>
@@ -9083,10 +9087,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9097,7 +9101,7 @@
         <v>35</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>34</v>
@@ -9106,19 +9110,19 @@
         <v>34</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9168,25 +9172,25 @@
         <v>34</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>34</v>
@@ -9197,10 +9201,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9211,7 +9215,7 @@
         <v>35</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>34</v>
@@ -9220,19 +9224,19 @@
         <v>34</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9282,25 +9286,25 @@
         <v>34</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>34</v>
@@ -9311,10 +9315,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9325,7 +9329,7 @@
         <v>35</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>34</v>
@@ -9334,16 +9338,16 @@
         <v>34</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9394,25 +9398,25 @@
         <v>34</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>34</v>
@@ -9423,10 +9427,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9437,7 +9441,7 @@
         <v>35</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>34</v>
@@ -9449,13 +9453,13 @@
         <v>34</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9506,13 +9510,13 @@
         <v>34</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>34</v>
@@ -9524,7 +9528,7 @@
         <v>34</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>34</v>
@@ -9535,14 +9539,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9561,16 +9565,16 @@
         <v>34</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9608,19 +9612,19 @@
         <v>34</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>35</v>
@@ -9629,16 +9633,16 @@
         <v>36</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>34</v>
@@ -9649,14 +9653,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9669,25 +9673,25 @@
         <v>34</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>34</v>
@@ -9736,7 +9740,7 @@
         <v>34</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>35</v>
@@ -9745,16 +9749,16 @@
         <v>36</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>34</v>
@@ -9765,10 +9769,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9776,10 +9780,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>34</v>
@@ -9788,19 +9792,19 @@
         <v>34</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9850,25 +9854,25 @@
         <v>34</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>34</v>
@@ -9879,10 +9883,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9893,7 +9897,7 @@
         <v>35</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>34</v>
@@ -9902,19 +9906,19 @@
         <v>34</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9964,25 +9968,25 @@
         <v>34</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>34</v>
@@ -9993,10 +9997,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10007,7 +10011,7 @@
         <v>35</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>34</v>
@@ -10016,19 +10020,19 @@
         <v>34</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10078,25 +10082,25 @@
         <v>34</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>34</v>
@@ -10107,10 +10111,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10121,7 +10125,7 @@
         <v>35</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>34</v>
@@ -10130,19 +10134,19 @@
         <v>34</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10192,25 +10196,25 @@
         <v>34</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>34</v>
@@ -10221,10 +10225,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10235,7 +10239,7 @@
         <v>35</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>34</v>
@@ -10244,19 +10248,19 @@
         <v>34</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10306,13 +10310,13 @@
         <v>34</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>34</v>
@@ -10324,7 +10328,7 @@
         <v>34</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>34</v>
@@ -10335,13 +10339,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>34</v>
@@ -10351,7 +10355,7 @@
         <v>35</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>34</v>
@@ -10360,16 +10364,16 @@
         <v>34</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10420,7 +10424,7 @@
         <v>34</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>35</v>
@@ -10429,16 +10433,16 @@
         <v>36</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>34</v>
@@ -10449,10 +10453,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10463,7 +10467,7 @@
         <v>35</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>34</v>
@@ -10475,13 +10479,13 @@
         <v>34</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10532,13 +10536,13 @@
         <v>34</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>34</v>
@@ -10550,7 +10554,7 @@
         <v>34</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>34</v>
@@ -10561,14 +10565,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -10587,16 +10591,16 @@
         <v>34</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -10634,19 +10638,19 @@
         <v>34</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>35</v>
@@ -10655,16 +10659,16 @@
         <v>36</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>34</v>
@@ -10675,14 +10679,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10695,25 +10699,25 @@
         <v>34</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>34</v>
@@ -10762,7 +10766,7 @@
         <v>34</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>35</v>
@@ -10771,16 +10775,16 @@
         <v>36</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>34</v>
@@ -10791,10 +10795,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10814,16 +10818,16 @@
         <v>34</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>34</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10874,7 +10878,7 @@
         <v>34</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>35</v>
@@ -10903,10 +10907,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10917,7 +10921,7 @@
         <v>35</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>34</v>
@@ -10926,19 +10930,19 @@
         <v>34</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10988,25 +10992,25 @@
         <v>34</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>34</v>
@@ -11017,10 +11021,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11031,7 +11035,7 @@
         <v>35</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>34</v>
@@ -11043,16 +11047,16 @@
         <v>34</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11102,25 +11106,25 @@
         <v>34</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>34</v>
@@ -11131,10 +11135,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11145,7 +11149,7 @@
         <v>35</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>34</v>
@@ -11154,16 +11158,16 @@
         <v>34</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11214,25 +11218,25 @@
         <v>34</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>34</v>
@@ -11243,10 +11247,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11257,7 +11261,7 @@
         <v>35</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>34</v>
@@ -11269,13 +11273,13 @@
         <v>34</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11326,13 +11330,13 @@
         <v>34</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>34</v>
@@ -11344,7 +11348,7 @@
         <v>34</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>34</v>
@@ -11355,14 +11359,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11381,16 +11385,16 @@
         <v>34</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11428,19 +11432,19 @@
         <v>34</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>35</v>
@@ -11449,16 +11453,16 @@
         <v>36</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>34</v>
@@ -11469,14 +11473,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11489,25 +11493,25 @@
         <v>34</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>34</v>
@@ -11556,7 +11560,7 @@
         <v>34</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>35</v>
@@ -11565,16 +11569,16 @@
         <v>36</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>34</v>
@@ -11585,10 +11589,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11599,7 +11603,7 @@
         <v>35</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>34</v>
@@ -11608,19 +11612,19 @@
         <v>34</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11646,13 +11650,13 @@
         <v>34</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>34</v>
@@ -11670,25 +11674,25 @@
         <v>34</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>34</v>
@@ -11699,10 +11703,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11713,7 +11717,7 @@
         <v>35</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>34</v>
@@ -11722,19 +11726,19 @@
         <v>34</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11784,25 +11788,25 @@
         <v>34</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>34</v>
@@ -11813,10 +11817,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11824,10 +11828,10 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>34</v>
@@ -11836,16 +11840,16 @@
         <v>34</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11896,25 +11900,25 @@
         <v>34</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>34</v>
@@ -11925,10 +11929,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11939,7 +11943,7 @@
         <v>35</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>34</v>
@@ -11951,13 +11955,13 @@
         <v>34</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12008,13 +12012,13 @@
         <v>34</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>34</v>
@@ -12026,7 +12030,7 @@
         <v>34</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>34</v>
@@ -12037,14 +12041,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12063,16 +12067,16 @@
         <v>34</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12110,19 +12114,19 @@
         <v>34</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>35</v>
@@ -12131,16 +12135,16 @@
         <v>36</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>34</v>
@@ -12151,14 +12155,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12171,25 +12175,25 @@
         <v>34</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>34</v>
@@ -12238,7 +12242,7 @@
         <v>34</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>35</v>
@@ -12247,16 +12251,16 @@
         <v>36</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>34</v>
@@ -12267,10 +12271,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12278,10 +12282,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>34</v>
@@ -12290,19 +12294,19 @@
         <v>34</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12313,7 +12317,7 @@
         <v>34</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>34</v>
@@ -12328,13 +12332,13 @@
         <v>34</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>34</v>
@@ -12352,25 +12356,25 @@
         <v>34</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>34</v>
@@ -12381,10 +12385,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12392,10 +12396,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>34</v>
@@ -12404,19 +12408,19 @@
         <v>34</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12427,7 +12431,7 @@
         <v>34</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>34</v>
@@ -12466,25 +12470,25 @@
         <v>34</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>34</v>
@@ -12495,10 +12499,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12509,7 +12513,7 @@
         <v>35</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>34</v>
@@ -12518,19 +12522,19 @@
         <v>34</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12580,25 +12584,25 @@
         <v>34</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>34</v>
@@ -12609,10 +12613,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12623,7 +12627,7 @@
         <v>35</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>34</v>
@@ -12632,19 +12636,19 @@
         <v>34</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12694,25 +12698,25 @@
         <v>34</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>34</v>
@@ -12723,10 +12727,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12737,7 +12741,7 @@
         <v>35</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>34</v>
@@ -12746,19 +12750,19 @@
         <v>34</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12808,25 +12812,25 @@
         <v>34</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>34</v>
@@ -12837,10 +12841,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12851,7 +12855,7 @@
         <v>35</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>34</v>
@@ -12860,19 +12864,19 @@
         <v>34</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12922,25 +12926,25 @@
         <v>34</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>34</v>
@@ -12951,10 +12955,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12965,7 +12969,7 @@
         <v>35</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>34</v>
@@ -12974,16 +12978,16 @@
         <v>34</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13034,25 +13038,25 @@
         <v>34</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>34</v>
@@ -13063,10 +13067,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13077,7 +13081,7 @@
         <v>35</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>34</v>
@@ -13089,13 +13093,13 @@
         <v>34</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13146,13 +13150,13 @@
         <v>34</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>34</v>
@@ -13164,7 +13168,7 @@
         <v>34</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>34</v>
@@ -13175,14 +13179,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13201,16 +13205,16 @@
         <v>34</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13248,19 +13252,19 @@
         <v>34</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>35</v>
@@ -13269,16 +13273,16 @@
         <v>36</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>34</v>
@@ -13289,14 +13293,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13309,25 +13313,25 @@
         <v>34</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>34</v>
@@ -13376,7 +13380,7 @@
         <v>34</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>35</v>
@@ -13385,16 +13389,16 @@
         <v>36</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>34</v>
@@ -13405,10 +13409,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13416,10 +13420,10 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>34</v>
@@ -13428,19 +13432,19 @@
         <v>34</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13490,25 +13494,25 @@
         <v>34</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>34</v>
@@ -13519,10 +13523,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13533,7 +13537,7 @@
         <v>35</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>34</v>
@@ -13542,19 +13546,19 @@
         <v>34</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13604,25 +13608,25 @@
         <v>34</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>34</v>
@@ -13633,10 +13637,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13647,7 +13651,7 @@
         <v>35</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>34</v>
@@ -13656,19 +13660,19 @@
         <v>34</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -13718,25 +13722,25 @@
         <v>34</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>34</v>
@@ -13747,10 +13751,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13761,7 +13765,7 @@
         <v>35</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>34</v>
@@ -13770,19 +13774,19 @@
         <v>34</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13832,25 +13836,25 @@
         <v>34</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>34</v>
@@ -13861,10 +13865,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13875,7 +13879,7 @@
         <v>35</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>34</v>
@@ -13884,19 +13888,19 @@
         <v>34</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13946,13 +13950,13 @@
         <v>34</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>34</v>
@@ -13964,7 +13968,7 @@
         <v>34</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>34</v>
@@ -13975,10 +13979,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13989,7 +13993,7 @@
         <v>35</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>34</v>
@@ -13998,22 +14002,22 @@
         <v>34</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>34</v>
@@ -14062,25 +14066,25 @@
         <v>34</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>34</v>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -473,11 +473,11 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:entry.request.url}
+    <t xml:space="preserve">profile:request.url}
 </t>
   </si>
   <si>
-    <t>Slice based on the entry.request.url pattern</t>
+    <t>Slice based on the request.url pattern</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1340,7 +1340,7 @@
     <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="25.04296875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="18.67578125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-23T10:14:09+00:00</t>
+    <t>2023-11-28T12:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -602,7 +602,7 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">profile:request.url}
+    <t xml:space="preserve">pattern:request.url}
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/main/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4094" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4094" uniqueCount="361">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -922,10 +922,6 @@
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
-  </si>
-  <si>
     <t>OBX</t>
   </si>
   <si>
@@ -1049,10 +1045,6 @@
   <si>
     <t>For the initial scope, this Device resource is only applicable to describe a single node in the containment tree that is produced by the context scanner in any medical device that implements or derives from the ISO/IEEE 11073 standard and that does not represent a metric. Examples for such a node are MDS, VMD, or Channel.
 With PHD medical units, there is no medical scanner and the unit is only a single node, a single 'simple' MDS, and it is static. Thus a PHD has no parent 'Device'.  When a PHD supports multiple device specializations, the single unit description is still the case. A specialization is just an way to organize a set of metric objects that tend to be generated by a single sensor, but the device could expose metric objects from several specializations which usually means it has more than one sensor. In PHDs multiple specialization support is rare.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Device</t>
@@ -7740,13 +7732,13 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK55" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AK55" t="s" s="2">
+      <c r="AL55" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7757,7 +7749,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>204</v>
@@ -7869,7 +7861,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>208</v>
@@ -7981,7 +7973,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>209</v>
@@ -8095,7 +8087,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>210</v>
@@ -8211,7 +8203,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>211</v>
@@ -8325,7 +8317,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>217</v>
@@ -8439,7 +8431,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>222</v>
@@ -8551,7 +8543,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>226</v>
@@ -8663,7 +8655,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>227</v>
@@ -8777,7 +8769,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>228</v>
@@ -8893,7 +8885,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>229</v>
@@ -8939,7 +8931,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9007,7 +8999,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>234</v>
@@ -9053,7 +9045,7 @@
         <v>77</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>77</v>
@@ -9121,7 +9113,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>238</v>
@@ -9235,7 +9227,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>241</v>
@@ -9349,7 +9341,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>244</v>
@@ -9463,7 +9455,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>247</v>
@@ -9577,7 +9569,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>250</v>
@@ -9689,7 +9681,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>254</v>
@@ -9801,7 +9793,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>255</v>
@@ -9915,7 +9907,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>256</v>
@@ -10031,7 +10023,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>257</v>
@@ -10145,7 +10137,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>260</v>
@@ -10259,7 +10251,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>263</v>
@@ -10373,7 +10365,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>267</v>
@@ -10487,7 +10479,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>271</v>
@@ -10601,13 +10593,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>183</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10715,7 +10707,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>189</v>
@@ -10827,7 +10819,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>190</v>
@@ -10941,7 +10933,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>191</v>
@@ -11057,7 +11049,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>192</v>
@@ -11169,7 +11161,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>195</v>
@@ -11283,7 +11275,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>199</v>
@@ -11309,16 +11301,16 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11380,13 +11372,13 @@
         <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>330</v>
+        <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11397,7 +11389,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>204</v>
@@ -11509,7 +11501,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>208</v>
@@ -11621,7 +11613,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>209</v>
@@ -11735,7 +11727,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>210</v>
@@ -11851,7 +11843,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>211</v>
@@ -11965,7 +11957,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>217</v>
@@ -12079,7 +12071,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>222</v>
@@ -12191,7 +12183,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>226</v>
@@ -12303,7 +12295,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>227</v>
@@ -12417,7 +12409,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>228</v>
@@ -12533,7 +12525,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>229</v>
@@ -12579,7 +12571,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -12647,7 +12639,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>234</v>
@@ -12693,7 +12685,7 @@
         <v>77</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>77</v>
@@ -12761,7 +12753,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>238</v>
@@ -12875,7 +12867,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>241</v>
@@ -12989,7 +12981,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>244</v>
@@ -13103,7 +13095,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>247</v>
@@ -13217,7 +13209,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>250</v>
@@ -13329,7 +13321,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>254</v>
@@ -13441,7 +13433,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>255</v>
@@ -13555,7 +13547,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>256</v>
@@ -13671,7 +13663,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>257</v>
@@ -13785,7 +13777,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>260</v>
@@ -13899,7 +13891,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>263</v>
@@ -14013,7 +14005,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>267</v>
@@ -14127,7 +14119,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>271</v>
@@ -14241,10 +14233,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14267,19 +14259,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14328,7 +14320,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
